--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -744,25 +744,7 @@
     <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1849,7 +1831,7 @@
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="89.6171875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -253,12 +259,6 @@
   </si>
   <si>
     <t>Mapping: SNOMED CT Attribute Binding</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -649,13 +649,13 @@
     <t>open</t>
   </si>
   <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
   </si>
   <si>
     <t>Observation.category:Laboratory</t>
@@ -729,6 +729,12 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -739,12 +745,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1824,14 +1824,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="89.6171875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="89.6171875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="107.01953125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="42.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2070,22 +2070,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="AN2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -2707,13 +2707,13 @@
         <v>84</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -2833,13 +2833,13 @@
         <v>84</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -2959,13 +2959,13 @@
         <v>84</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP9" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ9" t="s" s="2">
         <v>84</v>
@@ -3087,13 +3087,13 @@
         <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP10" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ10" t="s" s="2">
         <v>84</v>
@@ -3204,25 +3204,25 @@
         <v>106</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="AO11" t="s" s="2">
+      <c r="AQ11" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR11" t="s" s="2">
         <v>84</v>
@@ -3330,22 +3330,22 @@
         <v>106</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AN12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>84</v>
@@ -3456,22 +3456,22 @@
         <v>106</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AL13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -3582,25 +3582,25 @@
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR14" t="s" s="2">
         <v>84</v>
@@ -3708,7 +3708,7 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>84</v>
@@ -3717,13 +3717,13 @@
         <v>84</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>203</v>
@@ -3847,16 +3847,16 @@
         <v>84</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="AO16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ16" t="s" s="2">
-        <v>84</v>
+        <v>203</v>
       </c>
       <c r="AR16" t="s" s="2">
         <v>84</v>
@@ -3966,28 +3966,28 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AP17" t="s" s="2">
+      <c r="AR17" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4097,25 +4097,25 @@
         <v>227</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>229</v>
+        <v>84</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>230</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="AQ18" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>232</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -4226,19 +4226,19 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AO19" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ19" t="s" s="2">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -4348,25 +4348,25 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
         <v>84</v>
@@ -4476,25 +4476,25 @@
         <v>258</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
         <v>84</v>
@@ -4608,19 +4608,19 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR22" t="s" s="2">
         <v>84</v>
@@ -4728,25 +4728,25 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AP23" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AO23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -4859,25 +4859,25 @@
         <v>84</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR24" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR24" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4988,16 +4988,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AP25" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -5113,25 +5113,25 @@
         <v>84</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR26" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR26" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="27" hidden="true">
@@ -5244,16 +5244,16 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ27" t="s" s="2">
         <v>84</v>
@@ -5367,25 +5367,25 @@
         <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AP28" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP28" t="s" s="2">
+      <c r="AQ28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR28" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -5498,16 +5498,16 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AN29" t="s" s="2">
+      <c r="AP29" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ29" t="s" s="2">
         <v>84</v>
@@ -5621,25 +5621,25 @@
         <v>84</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AP30" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
+      <c r="AQ30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5747,25 +5747,25 @@
         <v>84</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
+      <c r="AQ31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR31" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AQ31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR31" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
@@ -5878,16 +5878,16 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO32" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AP32" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6005,13 +6005,13 @@
         <v>84</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6131,13 +6131,13 @@
         <v>84</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6259,13 +6259,13 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6380,16 +6380,16 @@
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6504,16 +6504,16 @@
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6629,19 +6629,19 @@
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AP38" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -6757,19 +6757,19 @@
         <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>84</v>
@@ -6889,13 +6889,13 @@
         <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -7010,16 +7010,16 @@
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
         <v>84</v>
@@ -7136,16 +7136,16 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -7262,16 +7262,16 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AP43" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -7390,16 +7390,16 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AP44" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -7517,13 +7517,13 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP45" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7643,13 +7643,13 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP46" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -7771,13 +7771,13 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -7893,22 +7893,22 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AM48" t="s" s="2">
+      <c r="AO48" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AQ48" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>84</v>
@@ -8021,25 +8021,25 @@
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AP49" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
+      <c r="AQ49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR49" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AQ49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR49" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -8152,16 +8152,16 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8277,25 +8277,25 @@
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AO51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR51" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8408,16 +8408,16 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO52" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AP52" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP52" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Abstract</t>
   </si>
   <si>
-    <t>false</t>
+    <t>true</t>
   </si>
   <si>
     <t>Derivation</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PATIENT (#2) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file PATIENT (2) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -729,7 +729,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1824,7 +1824,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="89.6171875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -732,7 +732,7 @@
     <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
